--- a/data/valuations/CSU_TO/CSU_TO_modelo_valoracion.xlsx
+++ b/data/valuations/CSU_TO/CSU_TO_modelo_valoracion.xlsx
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.2275</v>
+        <v>0.20125</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.20475</v>
+        <v>0.181125</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.182</v>
+        <v>0.161</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.15925</v>
+        <v>0.140875</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.1365</v>
+        <v>0.12075</v>
       </c>
     </row>
     <row r="10">
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.1225</v>
+        <v>0.14875</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.11025</v>
+        <v>0.133875</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.098</v>
+        <v>0.119</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.08574999999999999</v>
+        <v>0.104125</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.0735</v>
+        <v>0.08925</v>
       </c>
     </row>
     <row r="11">
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.3790010985749936</v>
+        <v>0.3690010985749936</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.3790010985749936</v>
+        <v>0.3690010985749936</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.3790010985749936</v>
+        <v>0.3690010985749936</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.3790010985749936</v>
+        <v>0.3690010985749936</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.3790010985749936</v>
+        <v>0.3690010985749936</v>
       </c>
     </row>
     <row r="17">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.3390010985749936</v>
+        <v>0.3490010985749936</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.3390010985749936</v>
+        <v>0.3490010985749936</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.3390010985749936</v>
+        <v>0.3490010985749936</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.3390010985749936</v>
+        <v>0.3490010985749936</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.3390010985749936</v>
+        <v>0.3490010985749936</v>
       </c>
     </row>
     <row r="18">
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.06293190923548418</v>
+        <v>0.06793190923548417</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.06293190923548418</v>
+        <v>0.06793190923548417</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.06293190923548418</v>
+        <v>0.06793190923548417</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.06293190923548418</v>
+        <v>0.06793190923548417</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.06293190923548418</v>
+        <v>0.06793190923548417</v>
       </c>
     </row>
     <row r="22">
@@ -912,19 +912,19 @@
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.08293190923548417</v>
+        <v>0.07793190923548418</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.08293190923548417</v>
+        <v>0.07793190923548418</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.08293190923548417</v>
+        <v>0.07793190923548418</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.08293190923548417</v>
+        <v>0.07793190923548418</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.08293190923548417</v>
+        <v>0.07793190923548418</v>
       </c>
     </row>
     <row r="23">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="28">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.0774</v>
+        <v>0.07729999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.0674</v>
+        <v>0.0673</v>
       </c>
     </row>
     <row r="37">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.0974</v>
+        <v>0.08729999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43">
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>2567.93</v>
+        <v>2499.22</v>
       </c>
     </row>
     <row r="4">
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/2567.93-1</f>
+        <f>C33/2499.22-1</f>
         <v/>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.0474</v>
+        <v>0.04729999999999999</v>
       </c>
       <c r="C39" s="22">
         <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*15/(1+$A$39)^5+$C$29)/$C$32</f>
@@ -3778,7 +3778,7 @@
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.05739999999999999</v>
+        <v>0.05729999999999999</v>
       </c>
       <c r="C40" s="22">
         <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*15/(1+$A$40)^5+$C$29)/$C$32</f>
@@ -3803,7 +3803,7 @@
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.0674</v>
+        <v>0.0673</v>
       </c>
       <c r="C41" s="22">
         <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*15/(1+$A$41)^5+$C$29)/$C$32</f>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.0774</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="C42" s="22">
         <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*15/(1+$A$42)^5+$C$29)/$C$32</f>
@@ -3853,7 +3853,7 @@
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.08739999999999999</v>
+        <v>0.08729999999999999</v>
       </c>
       <c r="C43" s="22">
         <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*15/(1+$A$43)^5+$C$29)/$C$32</f>
@@ -3878,7 +3878,7 @@
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.0974</v>
+        <v>0.0973</v>
       </c>
       <c r="C44" s="22">
         <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*15/(1+$A$44)^5+$C$29)/$C$32</f>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.1074</v>
+        <v>0.1073</v>
       </c>
       <c r="C45" s="22">
         <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*15/(1+$A$45)^5+$C$29)/$C$32</f>

--- a/data/valuations/CSU_TO/CSU_TO_modelo_valoracion.xlsx
+++ b/data/valuations/CSU_TO/CSU_TO_modelo_valoracion.xlsx
@@ -868,19 +868,19 @@
         </is>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.07293190923548418</v>
+        <v>0.1371994982996774</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.07293190923548418</v>
+        <v>0.1371994982996774</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.07293190923548418</v>
+        <v>0.1371994982996774</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.07293190923548418</v>
+        <v>0.1371994982996774</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.07293190923548418</v>
+        <v>0.1371994982996774</v>
       </c>
     </row>
     <row r="21">
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.06793190923548417</v>
+        <v>0.1321994982996774</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.06793190923548417</v>
+        <v>0.1321994982996774</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.06793190923548417</v>
+        <v>0.1321994982996774</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.06793190923548417</v>
+        <v>0.1321994982996774</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.06793190923548417</v>
+        <v>0.1321994982996774</v>
       </c>
     </row>
     <row r="22">
@@ -912,19 +912,19 @@
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.07793190923548418</v>
+        <v>0.1421994982996774</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.07793190923548418</v>
+        <v>0.1421994982996774</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.07793190923548418</v>
+        <v>0.1421994982996774</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.07793190923548418</v>
+        <v>0.1421994982996774</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.07793190923548418</v>
+        <v>0.1421994982996774</v>
       </c>
     </row>
     <row r="23">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -983,19 +983,19 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.005923761837990575</v>
+        <v>0.006020975916771943</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.005923761837990575</v>
+        <v>0.006020975916771943</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.005923761837990575</v>
+        <v>0.006020975916771943</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.005923761837990575</v>
+        <v>0.006020975916771943</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.005923761837990575</v>
+        <v>0.006020975916771943</v>
       </c>
     </row>
     <row r="32">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.07340000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.0673</v>
+        <v>0.06340000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.08729999999999999</v>
+        <v>0.0834</v>
       </c>
     </row>
     <row r="38">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41">
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="C41" s="9" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43">
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>2499.22</v>
+        <v>2358.89</v>
       </c>
     </row>
     <row r="4">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="K21" s="8">
-        <f>K12*$C$16</f>
+        <f>K8*$C$16</f>
         <v/>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/2499.22-1</f>
+        <f>C33/2358.89-1</f>
         <v/>
       </c>
     </row>
@@ -3727,202 +3727,202 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>15x</t>
+          <t>19x</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>17x</t>
+          <t>21x</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>19x</t>
+          <t>23x</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>21x</t>
+          <t>25x</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>23x</t>
+          <t>27x</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.04729999999999999</v>
+        <v>0.04340000000000001</v>
       </c>
       <c r="C39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*15/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*19/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*17/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*21/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*19/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*23/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*21/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*25/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*23/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*27/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.05729999999999999</v>
+        <v>0.0534</v>
       </c>
       <c r="C40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*15/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*19/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*17/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*21/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*19/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*23/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*21/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*25/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*23/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*27/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.0673</v>
+        <v>0.06340000000000001</v>
       </c>
       <c r="C41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*15/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*19/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*17/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*21/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*19/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*23/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*21/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*25/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*23/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*27/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="C42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*15/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*19/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*17/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*21/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*19/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*23/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*21/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*25/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*23/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*27/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.08729999999999999</v>
+        <v>0.0834</v>
       </c>
       <c r="C43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*15/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*19/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*17/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*21/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*19/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*23/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*21/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*25/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*23/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*27/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.0973</v>
+        <v>0.09340000000000001</v>
       </c>
       <c r="C44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*15/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*19/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*17/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*21/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*19/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*23/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*21/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*25/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*23/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*27/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.1073</v>
+        <v>0.1034</v>
       </c>
       <c r="C45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*15/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*19/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*17/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*21/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*19/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*23/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*21/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*25/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*23/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*27/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>

--- a/data/valuations/CSU_TO/CSU_TO_modelo_valoracion.xlsx
+++ b/data/valuations/CSU_TO/CSU_TO_modelo_valoracion.xlsx
@@ -519,7 +519,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Constellation Software Inc. (CSU.TO) - Assumptions</t>
+          <t>Constellation Software Inc. (CSU_TO) - Assumptions</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -868,19 +868,19 @@
         </is>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.1371994982996774</v>
+        <v>0.1776365627408716</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.1371994982996774</v>
+        <v>0.1776365627408716</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.1371994982996774</v>
+        <v>0.1776365627408716</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.1371994982996774</v>
+        <v>0.1776365627408716</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.1371994982996774</v>
+        <v>0.1776365627408716</v>
       </c>
     </row>
     <row r="21">
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.1321994982996774</v>
+        <v>0.1726365627408716</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.1321994982996774</v>
+        <v>0.1726365627408716</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.1321994982996774</v>
+        <v>0.1726365627408716</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.1321994982996774</v>
+        <v>0.1726365627408716</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.1321994982996774</v>
+        <v>0.1726365627408716</v>
       </c>
     </row>
     <row r="22">
@@ -912,19 +912,19 @@
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.1421994982996774</v>
+        <v>0.1826365627408716</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.1421994982996774</v>
+        <v>0.1826365627408716</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.1421994982996774</v>
+        <v>0.1826365627408716</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.1421994982996774</v>
+        <v>0.1826365627408716</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.1421994982996774</v>
+        <v>0.1826365627408716</v>
       </c>
     </row>
     <row r="23">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0732</v>
       </c>
     </row>
     <row r="36">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.06340000000000001</v>
+        <v>0.06320000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.0834</v>
+        <v>0.0832</v>
       </c>
     </row>
     <row r="38">
@@ -1243,7 +1243,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Constellation Software Inc. (CSU.TO) - Historical Financial Statements</t>
+          <t>Constellation Software Inc. (CSU_TO) - Historical Financial Statements</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1935,7 +1935,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Constellation Software Inc. (CSU.TO) - Financial Model</t>
+          <t>Constellation Software Inc. (CSU_TO) - Financial Model</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -3255,7 +3255,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Constellation Software Inc. (CSU.TO) - DCF Valuation</t>
+          <t>Constellation Software Inc. (CSU_TO) - DCF Valuation</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>2358.89</v>
+        <v>2441.27</v>
       </c>
     </row>
     <row r="4">
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/2358.89-1</f>
+        <f>C33/2441.27-1</f>
         <v/>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.04340000000000001</v>
+        <v>0.0432</v>
       </c>
       <c r="C39" s="22">
         <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*19/(1+$A$39)^5+$C$29)/$C$32</f>
@@ -3778,7 +3778,7 @@
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.0534</v>
+        <v>0.0532</v>
       </c>
       <c r="C40" s="22">
         <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*19/(1+$A$40)^5+$C$29)/$C$32</f>
@@ -3803,7 +3803,7 @@
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.06340000000000001</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="C41" s="22">
         <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*19/(1+$A$41)^5+$C$29)/$C$32</f>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0732</v>
       </c>
       <c r="C42" s="22">
         <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*19/(1+$A$42)^5+$C$29)/$C$32</f>
@@ -3853,7 +3853,7 @@
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.0834</v>
+        <v>0.0832</v>
       </c>
       <c r="C43" s="22">
         <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*19/(1+$A$43)^5+$C$29)/$C$32</f>
@@ -3878,7 +3878,7 @@
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.09340000000000001</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="C44" s="22">
         <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*19/(1+$A$44)^5+$C$29)/$C$32</f>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.1034</v>
+        <v>0.1032</v>
       </c>
       <c r="C45" s="22">
         <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*19/(1+$A$45)^5+$C$29)/$C$32</f>
